--- a/public/FNFUploader_final.xlsx
+++ b/public/FNFUploader_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v41797\Desktop\HRMS_FRONTEND\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F690BCEB-575E-4671-A096-A6B9BCF472AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992FAAB8-3611-4E73-ADD6-129116E145D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -215,12 +212,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,26 +559,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AJ2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25" customWidth="1"/>
-    <col min="34" max="34" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -596,10 +596,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -671,7 +671,7 @@
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
@@ -681,14 +681,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>45688</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>45672</v>
       </c>
       <c r="D2">
@@ -706,10 +706,10 @@
       <c r="H2">
         <v>5000</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>45383</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>45747</v>
       </c>
       <c r="K2">
@@ -781,7 +781,7 @@
       <c r="AG2" t="s">
         <v>39</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AH2" s="3">
         <v>45693</v>
       </c>
       <c r="AI2" t="s">
@@ -790,14 +790,6 @@
       <c r="AJ2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
